--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A435AD31-717F-427A-8E8C-EB23AACE8A4E}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81EC1994-0251-4E2F-982E-D388D142C635}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="61">
   <si>
     <t>S/N</t>
   </si>
@@ -155,6 +155,9 @@
     <t>Half Yearly(Jan and July)</t>
   </si>
   <si>
+    <t>Done on 07/15/2026</t>
+  </si>
+  <si>
     <t>Annual Electrical inspection</t>
   </si>
   <si>
@@ -198,6 +201,24 @@
   </si>
   <si>
     <t>CTO CRM (0.3 MTPA)</t>
+  </si>
+  <si>
+    <t>Testing put</t>
+  </si>
+  <si>
+    <t>CRM compliance put</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sayak </t>
+  </si>
+  <si>
+    <t>ruchita</t>
+  </si>
+  <si>
+    <t>Compiled</t>
   </si>
 </sst>
 </file>
@@ -739,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -903,7 +924,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="15">
-        <v>46170</v>
+        <v>46534</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>18</v>
@@ -929,7 +950,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="15">
-        <v>46148</v>
+        <v>46512</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>12</v>
@@ -1065,7 +1086,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="20.45">
+    <row r="13" spans="1:8" ht="23.25">
       <c r="A13" s="20">
         <v>12</v>
       </c>
@@ -1085,9 +1106,11 @@
         <v>30</v>
       </c>
       <c r="G13" s="23">
-        <v>46204</v>
-      </c>
-      <c r="H13" s="21"/>
+        <v>46569</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="20">
@@ -1097,13 +1120,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>29</v>
@@ -1112,7 +1135,7 @@
         <v>46387</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1123,7 +1146,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>10</v>
@@ -1138,7 +1161,7 @@
         <v>46468</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.45">
@@ -1146,25 +1169,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" s="23">
         <v>46436</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1175,20 +1198,20 @@
         <v>22</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="23">
         <v>46477</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1199,22 +1222,49 @@
         <v>22</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="23">
         <v>46477</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="11.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="23">
+        <v>46477</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="11.25"/>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1428,6 +1478,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1436,22 +1494,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81EC1994-0251-4E2F-982E-D388D142C635}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E6A160-78DE-4D3F-8081-9212F2E7E82F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
   <si>
     <t>S/N</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>Compiled</t>
+  </si>
+  <si>
+    <t>Testing 2.0</t>
+  </si>
+  <si>
+    <t>CRM compliance Final Test</t>
+  </si>
+  <si>
+    <t>Ruchita</t>
   </si>
 </sst>
 </file>
@@ -255,7 +264,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -265,104 +274,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -370,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -379,7 +300,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -389,42 +319,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -443,18 +342,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -774,497 +661,523 @@
     <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" ht="11.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4">
+    <row r="2" spans="1:8" ht="11.25">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>46485</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4">
+    <row r="3" spans="1:8" ht="11.25">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>46317</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
+    <row r="4" spans="1:8" ht="11.25">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>46284</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
+    <row r="5" spans="1:8" ht="11.25">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>46385</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="41.45" thickBot="1">
-      <c r="A6" s="10">
+    <row r="6" spans="1:8" ht="46.5">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="11">
         <v>46534</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21" thickBot="1">
-      <c r="A7" s="16">
+    <row r="7" spans="1:8" ht="23.25">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="11">
         <v>46512</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="20">
+    <row r="8" spans="1:8" ht="11.25">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="15">
         <v>46295</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="20">
+    <row r="9" spans="1:8" ht="11.25">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="15">
         <v>46246</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="20">
+    <row r="10" spans="1:8" ht="11.25">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="15">
         <v>46246</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="20">
+    <row r="11" spans="1:8" ht="11.25">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="15">
         <v>46246</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.45">
-      <c r="A12" s="20">
+    <row r="12" spans="1:8" ht="23.25">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="23.25">
-      <c r="A13" s="20">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="15">
         <v>46569</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="20">
+    <row r="14" spans="1:8" ht="11.25">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="15">
         <v>46387</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="20">
+    <row r="15" spans="1:8" ht="11.25">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="15">
         <v>46468</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="20.45">
-      <c r="A16" s="20">
+    <row r="16" spans="1:8" ht="23.25">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="15">
         <v>46436</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="20">
+    <row r="17" spans="1:8" ht="11.25">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="25" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="15">
         <v>46477</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="20">
+    <row r="18" spans="1:8" ht="11.25">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="25" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="15">
         <v>46477</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="13" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="11.25">
-      <c r="A19" s="1">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="15">
         <v>46477</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="11.25"/>
+    <row r="20" spans="1:8" ht="11.25">
+      <c r="A20" s="14">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="15">
+        <v>46477</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="11.25"/>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1273,6 +1186,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1477,14 +1398,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1495,11 +1408,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E6A160-78DE-4D3F-8081-9212F2E7E82F}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF97D6D-0686-4FD3-ADC1-6BF31EBF49C1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
   <si>
     <t>S/N</t>
   </si>
@@ -201,33 +201,6 @@
   </si>
   <si>
     <t>CTO CRM (0.3 MTPA)</t>
-  </si>
-  <si>
-    <t>Testing put</t>
-  </si>
-  <si>
-    <t>CRM compliance put</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sayak </t>
-  </si>
-  <si>
-    <t>ruchita</t>
-  </si>
-  <si>
-    <t>Compiled</t>
-  </si>
-  <si>
-    <t>Testing 2.0</t>
-  </si>
-  <si>
-    <t>CRM compliance Final Test</t>
-  </si>
-  <si>
-    <t>Ruchita</t>
   </si>
 </sst>
 </file>
@@ -1126,56 +1099,24 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="11.25">
-      <c r="A19" s="14">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="15">
-        <v>46477</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>60</v>
-      </c>
+      <c r="A19" s="14"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" ht="11.25">
-      <c r="A20" s="14">
-        <v>19</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="15">
-        <v>46477</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>60</v>
-      </c>
+      <c r="A20" s="14"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" ht="11.25"/>
   </sheetData>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF97D6D-0686-4FD3-ADC1-6BF31EBF49C1}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B397DE2E-ACD7-46C6-AB5E-542F1933604F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
   <si>
     <t>S/N</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Stamping of Weighing scales</t>
-  </si>
-  <si>
-    <t>As per excel sheet</t>
   </si>
   <si>
     <t>Complied.
@@ -939,11 +936,11 @@
       <c r="F12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="15">
+        <v>46477</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="23.25">
@@ -954,10 +951,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>38</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>29</v>
@@ -969,7 +966,7 @@
         <v>46569</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="11.25">
@@ -980,13 +977,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>29</v>
@@ -995,7 +992,7 @@
         <v>46387</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="11.25">
@@ -1006,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>10</v>
@@ -1021,7 +1018,7 @@
         <v>46468</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="23.25">
@@ -1029,25 +1026,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="E16" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>48</v>
-      </c>
       <c r="F16" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="15">
         <v>46436</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="11.25">
@@ -1058,20 +1055,20 @@
         <v>22</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="G17" s="15">
         <v>46477</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="11.25">
@@ -1082,20 +1079,20 @@
         <v>22</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="G18" s="15">
         <v>46477</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="11.25">
@@ -1127,11 +1124,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1340,16 +1338,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1357,5 +1354,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B397DE2E-ACD7-46C6-AB5E-542F1933604F}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22426389-EF23-46EF-888E-02B1E71C5C6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
   <si>
     <t>S/N</t>
   </si>
@@ -198,6 +198,18 @@
   </si>
   <si>
     <t>CTO CRM (0.3 MTPA)</t>
+  </si>
+  <si>
+    <t>CRM Mechanical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural stability </t>
+  </si>
+  <si>
+    <t>Trienniel</t>
+  </si>
+  <si>
+    <t>30.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1096,13 +1108,27 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="11.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="A19" s="14">
+        <v>18</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" ht="11.25">
@@ -1124,15 +1150,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1337,6 +1354,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1346,11 +1372,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22426389-EF23-46EF-888E-02B1E71C5C6E}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6893D0FE-1F27-4971-9FE6-887AAEA554C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
   <si>
     <t>S/N</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>30.10.2026</t>
+  </si>
+  <si>
+    <t>1st time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rail alignment </t>
   </si>
 </sst>
 </file>
@@ -1129,12 +1135,20 @@
       <c r="G19" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="11.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="14"/>
+      <c r="A20" s="14">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>59</v>
+      </c>
       <c r="D20" s="17"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6893D0FE-1F27-4971-9FE6-887AAEA554C5}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00361389-AFDC-4ABB-8ECD-9B102AF351AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
   <si>
     <t>S/N</t>
   </si>
@@ -215,7 +215,7 @@
     <t>1st time</t>
   </si>
   <si>
-    <t xml:space="preserve">Rail alignment </t>
+    <t>Rail alignment of EOT cranes</t>
   </si>
 </sst>
 </file>
@@ -1150,8 +1150,12 @@
         <v>59</v>
       </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G20" s="15"/>
       <c r="H20" s="13"/>
     </row>
@@ -1164,6 +1168,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1368,25 +1389,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1394,5 +1398,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00361389-AFDC-4ABB-8ECD-9B102AF351AF}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92E613DD-5545-4A90-9E29-A926803AB2A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,7 +329,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -659,7 +659,7 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -685,7 +685,7 @@
       <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="10" t="s">
@@ -711,7 +711,7 @@
       <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="10" t="s">
@@ -737,7 +737,7 @@
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="10" t="s">
@@ -763,7 +763,7 @@
       <c r="C5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="10" t="s">
@@ -789,7 +789,7 @@
       <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="10" t="s">
@@ -815,7 +815,7 @@
       <c r="C7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="14" t="s">
@@ -841,7 +841,7 @@
       <c r="C8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="17" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="14" t="s">
@@ -867,7 +867,7 @@
       <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="17" t="s">
@@ -893,7 +893,7 @@
       <c r="C10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -919,7 +919,7 @@
       <c r="C11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -945,7 +945,7 @@
       <c r="C12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -1075,7 +1075,7 @@
       <c r="C17" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="12"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="17" t="s">
         <v>50</v>
       </c>
@@ -1099,7 +1099,7 @@
       <c r="C18" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="17" t="s">
         <v>50</v>
       </c>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92E613DD-5545-4A90-9E29-A926803AB2A5}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8E5780-2CCA-42A3-A2A9-8C7E33831E99}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,7 +753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="11.25">
+    <row r="5" spans="1:8" ht="13.5" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1168,23 +1168,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1389,8 +1372,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1398,5 +1398,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8E5780-2CCA-42A3-A2A9-8C7E33831E99}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B345D8CC-6762-45E9-B308-A8C7DD1CF2C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="64">
   <si>
     <t>S/N</t>
   </si>
@@ -216,6 +216,18 @@
   </si>
   <si>
     <t>Rail alignment of EOT cranes</t>
+  </si>
+  <si>
+    <t>Charging consent Hydrogen plant</t>
+  </si>
+  <si>
+    <t>First time</t>
+  </si>
+  <si>
+    <t>Charging consent ZLD plant</t>
+  </si>
+  <si>
+    <t>Charging consent BA 5/6  lines</t>
   </si>
 </sst>
 </file>
@@ -635,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1159,7 +1171,46 @@
       <c r="G20" s="15"/>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" spans="1:8" ht="11.25"/>
+    <row r="21" spans="1:8" ht="11.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="C22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="C23" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="C24" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="C25" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B345D8CC-6762-45E9-B308-A8C7DD1CF2C9}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8E9C49B-E9BC-4ABB-8DF7-5D700FFAEE2B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
   <si>
     <t>S/N</t>
   </si>
@@ -218,16 +218,31 @@
     <t>Rail alignment of EOT cranes</t>
   </si>
   <si>
-    <t>Charging consent Hydrogen plant</t>
+    <t>Charging consent Hydrogen plant from CEI</t>
   </si>
   <si>
     <t>First time</t>
   </si>
   <si>
-    <t>Charging consent ZLD plant</t>
-  </si>
-  <si>
-    <t>Charging consent BA 5/6  lines</t>
+    <t>Charging consent ZLD plant from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent BA 5/6  lines from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent Mill-3 from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent Mill-4 from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent of LMO trafo and CGPL line from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent of IDCW from CEI</t>
+  </si>
+  <si>
+    <t>Charging consent of quality lab from CEI</t>
   </si>
 </sst>
 </file>
@@ -264,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -287,11 +302,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -342,6 +370,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1152,64 +1190,158 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="11.25">
-      <c r="A20" s="14">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="20"/>
+      <c r="E20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="13"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
     </row>
     <row r="21" spans="1:8" ht="11.25">
-      <c r="A21" s="1">
+      <c r="A21" s="14">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="14" t="s">
         <v>51</v>
       </c>
+      <c r="G21" s="17"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="C22" s="1" t="s">
+      <c r="A22" s="14">
+        <v>21</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>62</v>
       </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="C23" s="1" t="s">
+      <c r="A23" s="14">
+        <v>22</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>63</v>
       </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="13"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="A24" s="14">
+        <v>23</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="C25" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="A25" s="14">
+        <v>24</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="13"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="14">
+        <v>25</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="13"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="14">
+        <v>26</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="14">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1219,6 +1351,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1423,15 +1564,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1441,11 +1573,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8E9C49B-E9BC-4ABB-8DF7-5D700FFAEE2B}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C7646A4-C13D-4E02-83DC-0805FDFC035B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="69">
   <si>
     <t>S/N</t>
   </si>
@@ -1241,9 +1241,15 @@
       <c r="C22" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="D22" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G22" s="17"/>
       <c r="H22" s="13"/>
     </row>
@@ -1257,9 +1263,15 @@
       <c r="C23" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G23" s="17"/>
       <c r="H23" s="13"/>
     </row>
@@ -1273,9 +1285,15 @@
       <c r="C24" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G24" s="17"/>
       <c r="H24" s="13"/>
     </row>
@@ -1289,9 +1307,15 @@
       <c r="C25" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="D25" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G25" s="17"/>
       <c r="H25" s="13"/>
     </row>
@@ -1305,9 +1329,15 @@
       <c r="C26" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="D26" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G26" s="17"/>
       <c r="H26" s="13"/>
     </row>
@@ -1321,9 +1351,15 @@
       <c r="C27" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
+      <c r="D27" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G27" s="17"/>
       <c r="H27" s="13"/>
     </row>
@@ -1337,9 +1373,15 @@
       <c r="C28" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="D28" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="G28" s="17"/>
       <c r="H28" s="13"/>
     </row>
@@ -1351,15 +1393,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1564,7 +1597,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
@@ -1572,14 +1605,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C7646A4-C13D-4E02-83DC-0805FDFC035B}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3673D64-9798-4AE8-B379-807FB01FEF3C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
   <si>
     <t>S/N</t>
   </si>
@@ -224,7 +224,13 @@
     <t>First time</t>
   </si>
   <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
     <t>Charging consent ZLD plant from CEI</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
   <si>
     <t>Charging consent BA 5/6  lines from CEI</t>
@@ -1228,10 +1234,14 @@
       <c r="F21" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="G21" s="15">
+        <v>46207</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="11.25">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -1239,7 +1249,7 @@
         <v>27</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>61</v>
@@ -1250,8 +1260,12 @@
       <c r="F22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="13"/>
+      <c r="G22" s="15">
+        <v>46207</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="14">
@@ -1261,7 +1275,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>61</v>
@@ -1283,7 +1297,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>61</v>
@@ -1305,7 +1319,7 @@
         <v>27</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>61</v>
@@ -1327,7 +1341,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>61</v>
@@ -1349,7 +1363,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>61</v>
@@ -1371,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>61</v>
@@ -1393,6 +1407,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1597,7 +1620,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
@@ -1605,23 +1628,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3673D64-9798-4AE8-B379-807FB01FEF3C}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB29553-A0A8-4F59-87A7-8977B3F7E64D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
   <si>
     <t>S/N</t>
   </si>
@@ -224,13 +224,10 @@
     <t>First time</t>
   </si>
   <si>
-    <t xml:space="preserve">Done </t>
+    <t>Done on 7/4/2026</t>
   </si>
   <si>
     <t>Charging consent ZLD plant from CEI</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>Charging consent BA 5/6  lines from CEI</t>
@@ -1235,7 +1232,7 @@
         <v>51</v>
       </c>
       <c r="G21" s="15">
-        <v>46207</v>
+        <v>46571</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>62</v>
@@ -1261,10 +1258,10 @@
         <v>51</v>
       </c>
       <c r="G22" s="15">
-        <v>46207</v>
+        <v>46571</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1275,7 +1272,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>61</v>
@@ -1297,7 +1294,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>61</v>
@@ -1319,7 +1316,7 @@
         <v>27</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>61</v>
@@ -1341,7 +1338,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>61</v>
@@ -1363,7 +1360,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>61</v>
@@ -1385,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>61</v>
